--- a/examples/xlsx/sample.xlsx
+++ b/examples/xlsx/sample.xlsx
@@ -16,31 +16,31 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
+    <t>M-1002</t>
+  </si>
+  <si>
+    <t>电流互感器</t>
+  </si>
+  <si>
+    <t>物料编码</t>
+  </si>
+  <si>
+    <t>物料名称</t>
+  </si>
+  <si>
+    <t>库存数量</t>
+  </si>
+  <si>
+    <t>温湿度传感器</t>
+  </si>
+  <si>
+    <t>边缘网关</t>
+  </si>
+  <si>
+    <t>M-1003</t>
+  </si>
+  <si>
     <t>M-1001</t>
-  </si>
-  <si>
-    <t>库存数量</t>
-  </si>
-  <si>
-    <t>温湿度传感器</t>
-  </si>
-  <si>
-    <t>M-1002</t>
-  </si>
-  <si>
-    <t>边缘网关</t>
-  </si>
-  <si>
-    <t>M-1003</t>
-  </si>
-  <si>
-    <t>电流互感器</t>
-  </si>
-  <si>
-    <t>物料编码</t>
-  </si>
-  <si>
-    <t>物料名称</t>
   </si>
 </sst>
 </file>
@@ -349,21 +349,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C2">
         <v>120</v>
@@ -371,10 +371,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C3">
         <v>35</v>
@@ -382,10 +382,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C4">
         <v>480</v>

--- a/examples/xlsx/sample.xlsx
+++ b/examples/xlsx/sample.xlsx
@@ -16,9 +16,21 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
+    <t>库存数量</t>
+  </si>
+  <si>
+    <t>M-1001</t>
+  </si>
+  <si>
+    <t>温湿度传感器</t>
+  </si>
+  <si>
     <t>M-1002</t>
   </si>
   <si>
+    <t>边缘网关</t>
+  </si>
+  <si>
     <t>电流互感器</t>
   </si>
   <si>
@@ -28,19 +40,7 @@
     <t>物料名称</t>
   </si>
   <si>
-    <t>库存数量</t>
-  </si>
-  <si>
-    <t>温湿度传感器</t>
-  </si>
-  <si>
-    <t>边缘网关</t>
-  </si>
-  <si>
     <t>M-1003</t>
-  </si>
-  <si>
-    <t>M-1001</t>
   </si>
 </sst>
 </file>
@@ -349,21 +349,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C2">
         <v>120</v>
@@ -371,10 +371,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C3">
         <v>35</v>
@@ -382,10 +382,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C4">
         <v>480</v>

--- a/examples/xlsx/sample.xlsx
+++ b/examples/xlsx/sample.xlsx
@@ -16,31 +16,31 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
+    <t>物料名称</t>
+  </si>
+  <si>
+    <t>M-1001</t>
+  </si>
+  <si>
+    <t>温湿度传感器</t>
+  </si>
+  <si>
+    <t>边缘网关</t>
+  </si>
+  <si>
+    <t>M-1003</t>
+  </si>
+  <si>
+    <t>电流互感器</t>
+  </si>
+  <si>
+    <t>物料编码</t>
+  </si>
+  <si>
     <t>库存数量</t>
   </si>
   <si>
-    <t>M-1001</t>
-  </si>
-  <si>
-    <t>温湿度传感器</t>
-  </si>
-  <si>
     <t>M-1002</t>
-  </si>
-  <si>
-    <t>边缘网关</t>
-  </si>
-  <si>
-    <t>电流互感器</t>
-  </si>
-  <si>
-    <t>物料编码</t>
-  </si>
-  <si>
-    <t>物料名称</t>
-  </si>
-  <si>
-    <t>M-1003</t>
   </si>
 </sst>
 </file>
@@ -352,10 +352,10 @@
         <v>6</v>
       </c>
       <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
         <v>7</v>
-      </c>
-      <c r="C1" t="s">
-        <v>0</v>
       </c>
     </row>
     <row r="2">
@@ -371,10 +371,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
         <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
       </c>
       <c r="C3">
         <v>35</v>
@@ -382,7 +382,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
         <v>5</v>
